--- a/ExportExcel/web PLT slution .xlsx
+++ b/ExportExcel/web PLT slution .xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
   <si>
     <t>STT</t>
   </si>
@@ -38,10 +38,33 @@
     <t/>
   </si>
   <si>
-    <t>SKIPPED</t>
-  </si>
-  <si>
-    <t>0 ms</t>
+    <t>FAILED</t>
+  </si>
+  <si>
+    <t>496 ms</t>
+  </si>
+  <si>
+    <t>unknown error: net::ERR_NAME_NOT_RESOLVED
+  (Session info: chrome=134.0.6998.178)
+Build info: version: '4.28.1', revision: '73f5ad48a2'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '22.0.1'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Command: [9c28490d3329116d2d9950fdf4b0b431, get {url=http://your-real-contact-page-url.com/contact}]
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 134.0.6998.178, chrome: {chromedriverVersion: 134.0.6998.165 (fd886e2cb29..., userDataDir: C:\Users\A\AppData\Local\Te...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:61605}, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:61605/devtoo..., se:cdpVersion: 134.0.6998.178, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 9c28490d3329116d2d9950fdf4b0b431</t>
+  </si>
+  <si>
+    <t>535 ms</t>
+  </si>
+  <si>
+    <t>unknown error: net::ERR_NAME_NOT_RESOLVED
+  (Session info: chrome=134.0.6998.178)
+Build info: version: '4.28.1', revision: '73f5ad48a2'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '22.0.1'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Command: [6a2a99fdf5c05a49610218f800788c1b, get {url=http://your-real-contact-page-url.com/contact}]
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 134.0.6998.178, chrome: {chromedriverVersion: 134.0.6998.165 (fd886e2cb29..., userDataDir: C:\Users\A\AppData\Local\Te...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:61625}, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:61625/devtoo..., se:cdpVersion: 134.0.6998.178, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 6a2a99fdf5c05a49610218f800788c1b</t>
   </si>
 </sst>
 </file>
@@ -114,9 +137,9 @@
     <col min="1" max="1" width="3.76171875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="14.4453125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="9.52734375" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="7.57421875" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="6.484375" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="13.2109375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="18.703125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="255.0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -149,14 +172,14 @@
       <c r="C2" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D2" t="s" s="0">
+      <c r="D2" t="s" s="2">
         <v>8</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>9</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -169,14 +192,14 @@
       <c r="C3" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D3" t="s" s="0">
+      <c r="D3" t="s" s="2">
         <v>8</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
